--- a/output/intraday/D2_riepilogo_intraday_2026-05-16.xlsx
+++ b/output/intraday/D2_riepilogo_intraday_2026-05-16.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,382 +433,382 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Gain_%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Price_Gain_Giorno</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Volume_Gain_Giorno</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>GAP_%</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Short Float</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Insider Own</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Inst Own</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Float Shares</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Shares Outstanding</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>VWAP_0930</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TimeHigh</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TimeLow</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>OpenPM</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>HighPM</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>LowPM</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ClosePM</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>VolumePM</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TimePMH</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>High_1m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Low_1m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Volume_1m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Close_1m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>High_5m</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Low_5m</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Volume_5m</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Close_5m</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>High_15m</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Low_15m</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Volume_15m</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Close_15m</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>High_30m</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Low_30m</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Volume_30m</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Close_30m</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>High_45m</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Low_45m</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Volume_45m</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Close_45m</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>High_60m</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Low_60m</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Volume_60m</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Close_60m</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>High_90m</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Low_90m</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Volume_90m</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Close_90m</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>High_120m</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Low_120m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Volume_120m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Close_120m</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>High_240m</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Low_240m</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Volume_240m</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Close_240m</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Close_0930</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Close_1000</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Close_1030</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Close_1100</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>Close_1130</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Close_1200</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Close_1230</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Close_1300</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Close_1330</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Close_1400</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>Close_1430</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Close_1500</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Close_1530</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Close_1600</t>
         </is>
@@ -808,21 +820,45 @@
           <t>LESL</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>32760000</v>
+      </c>
       <c r="D2" t="n">
         <v>145</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41182593</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10.59%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>60.44%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>9124397</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9359448</v>
+      </c>
       <c r="M2" t="n">
         <v>3.81</v>
       </c>
@@ -1028,21 +1064,43 @@
           <t>DXF</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>2750000</v>
+      </c>
       <c r="D3" t="n">
         <v>130</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>95552005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-23.43</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4.96%</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>3227419</v>
+      </c>
       <c r="M3" t="n">
         <v>1.34</v>
       </c>
@@ -1248,21 +1306,45 @@
           <t>QUCY</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>37550000</v>
+      </c>
       <c r="D4" t="n">
         <v>124</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>266890083</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8.99%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14.69%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>10846040</v>
+      </c>
+      <c r="L4" t="n">
+        <v>12515335</v>
+      </c>
       <c r="M4" t="n">
         <v>2.52</v>
       </c>
@@ -1468,21 +1550,45 @@
           <t>YMAT</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>32160000</v>
+      </c>
       <c r="D5" t="n">
         <v>119</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27996378</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.81%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>85.35%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2403284</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13953333</v>
+      </c>
       <c r="M5" t="n">
         <v>2</v>
       </c>
@@ -1688,21 +1794,45 @@
           <t>AIIO</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>110570000</v>
+      </c>
       <c r="D6" t="n">
         <v>116</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="F6" t="n">
+        <v>163208365</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-23.58</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>75.01%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>9284938</v>
+      </c>
+      <c r="L6" t="n">
+        <v>17966028</v>
+      </c>
       <c r="M6" t="n">
         <v>4.58</v>
       </c>
@@ -1908,21 +2038,45 @@
           <t>SNAL</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>46030000</v>
+      </c>
       <c r="D7" t="n">
         <v>115</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F7" t="n">
+        <v>275305929</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>11.46%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>68.81%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>12192450</v>
+      </c>
+      <c r="L7" t="n">
+        <v>13873422</v>
+      </c>
       <c r="M7" t="n">
         <v>1.2</v>
       </c>
@@ -2128,21 +2282,45 @@
           <t>MOBX</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>33110000</v>
+      </c>
       <c r="D8" t="n">
         <v>79</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>157927528</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-17.68</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>16.12%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30.42%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7.12%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>8365534</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10444355</v>
+      </c>
       <c r="M8" t="n">
         <v>2.65</v>
       </c>
@@ -2348,21 +2526,43 @@
           <t>YOOV</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>276920000</v>
+      </c>
       <c r="D9" t="n">
         <v>76</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>61043065</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>19.32%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>206674356</v>
+      </c>
       <c r="M9" t="n">
         <v>1.12</v>
       </c>
